--- a/tools/excel/3xlsx/item.xlsx
+++ b/tools/excel/3xlsx/item.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -516,6 +516,21 @@
           <t>排序权重</t>
         </is>
       </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>购买货币</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>购买价格</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>商店分类</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -578,6 +593,21 @@
           <t>sortPriority</t>
         </is>
       </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>priceType</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>shopCategory</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -640,6 +670,21 @@
           <t>int</t>
         </is>
       </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>uint</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>uint</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -698,6 +743,21 @@
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>all</t>
         </is>
@@ -716,6 +776,9 @@
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -730,6 +793,9 @@
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -762,7 +828,6 @@
       <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>20</v>
       </c>
@@ -771,6 +836,15 @@
       </c>
       <c r="L7" t="n">
         <v>100</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -804,7 +878,6 @@
       <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>10</v>
       </c>
@@ -813,6 +886,15 @@
       </c>
       <c r="L8" t="n">
         <v>110</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>80</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -846,7 +928,6 @@
       <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>20</v>
       </c>
@@ -855,6 +936,15 @@
       </c>
       <c r="L9" t="n">
         <v>90</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -888,7 +978,6 @@
       <c r="H10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>1</v>
       </c>
@@ -897,6 +986,15 @@
       </c>
       <c r="L10" t="n">
         <v>520</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>240</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -930,7 +1028,6 @@
       <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>1</v>
       </c>
@@ -939,6 +1036,15 @@
       </c>
       <c r="L11" t="n">
         <v>510</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -972,7 +1078,6 @@
       <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>50</v>
       </c>
@@ -981,6 +1086,15 @@
       </c>
       <c r="L12" t="n">
         <v>60</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1014,7 +1128,6 @@
       <c r="H13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>50</v>
       </c>
@@ -1023,6 +1136,15 @@
       </c>
       <c r="L13" t="n">
         <v>50</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1070,6 +1192,15 @@
       <c r="L14" t="n">
         <v>800</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1116,6 +1247,15 @@
       <c r="L15" t="n">
         <v>70</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>180</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1148,7 +1288,6 @@
       <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
         <v>999</v>
       </c>
@@ -1157,6 +1296,15 @@
       </c>
       <c r="L16" t="n">
         <v>10</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/3xlsx/item.xlsx
+++ b/tools/excel/3xlsx/item.xlsx
@@ -838,7 +838,7 @@
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>30</v>
@@ -888,7 +888,7 @@
         <v>110</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>80</v>
@@ -938,7 +938,7 @@
         <v>90</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>50</v>
@@ -988,7 +988,7 @@
         <v>520</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>240</v>
@@ -1038,7 +1038,7 @@
         <v>510</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -1088,7 +1088,7 @@
         <v>60</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1138,7 +1138,7 @@
         <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1193,7 +1193,7 @@
         <v>800</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>180</v>
@@ -1298,7 +1298,7 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>

--- a/tools/excel/3xlsx/item.xlsx
+++ b/tools/excel/3xlsx/item.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -531,6 +531,11 @@
           <t>商店分类</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>模型路径</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -608,6 +613,11 @@
           <t>shopCategory</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>modelPath</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -685,6 +695,11 @@
           <t>uint</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -760,6 +775,11 @@
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>all</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>client</t>
         </is>
       </c>
     </row>
@@ -1307,6 +1327,226 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6001</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>突击步枪</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>全自动突击步枪，射速快、弹量足。</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UI/Item/sword_iron</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>300</v>
+      </c>
+      <c r="L17" t="n">
+        <v>600</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>600</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Weapon/AssaultRifle1_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6002</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>狙击枪</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>高倍远程狙击枪，单发高伤。</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UI/Item/sword_iron</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>500</v>
+      </c>
+      <c r="L18" t="n">
+        <v>590</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Weapon/SniperRifle1_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6003</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>霰弹枪</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>近距离散射霰弹枪，火力凶猛。</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UI/Item/sword_iron</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>350</v>
+      </c>
+      <c r="L19" t="n">
+        <v>580</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>700</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Weapon/Shotgun1_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6004</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>手枪</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>轻便副武器手枪，出枪迅速。</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UI/Item/sword_iron</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>150</v>
+      </c>
+      <c r="L20" t="n">
+        <v>570</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>300</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Weapon/Pistol1_01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/excel/3xlsx/item.xlsx
+++ b/tools/excel/3xlsx/item.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -864,7 +864,7 @@
         <v>30</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -914,7 +914,7 @@
         <v>80</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -964,7 +964,7 @@
         <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1014,7 +1014,7 @@
         <v>240</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1064,7 +1064,7 @@
         <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1274,7 +1274,7 @@
         <v>180</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1545,6 +1545,276 @@
         <is>
           <t>Weapon/Pistol1_01</t>
         </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7001</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>红点瞄准镜</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>红点全息,快速锁定近距目标。</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>150</v>
+      </c>
+      <c r="L21" t="n">
+        <v>530</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>200</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7002</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>四倍瞄准镜</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中距离 4 倍变焦,平衡之选。</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>350</v>
+      </c>
+      <c r="L22" t="n">
+        <v>520</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>500</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7003</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>八倍瞄准镜</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>远距离 8 倍高倍镜,狙击利器。</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>700</v>
+      </c>
+      <c r="L23" t="n">
+        <v>510</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8001</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>标准弹药</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>通用弹药,弹匣容量 12 发。</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>12</v>
+      </c>
+      <c r="K24" t="n">
+        <v>80</v>
+      </c>
+      <c r="L24" t="n">
+        <v>530</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>100</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8002</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>穿甲弹</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>高穿透弹药,弹匣容量 20 发。</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>20</v>
+      </c>
+      <c r="K25" t="n">
+        <v>200</v>
+      </c>
+      <c r="L25" t="n">
+        <v>520</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>300</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>8003</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>高爆弹</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>高伤害弹药,弹匣容量 30 发。</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>30</v>
+      </c>
+      <c r="K26" t="n">
+        <v>400</v>
+      </c>
+      <c r="L26" t="n">
+        <v>510</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>600</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/3xlsx/item.xlsx
+++ b/tools/excel/3xlsx/item.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>霰弹枪</t>
+          <t>散弹枪</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>近距离散射霰弹枪，火力凶猛。</t>
+          <t>近距离散射,火力凶猛。</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1817,6 +1817,7 @@
         <v>3</v>
       </c>
     </row>
+    <row r="27"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/excel/3xlsx/item.xlsx
+++ b/tools/excel/3xlsx/item.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>红点瞄准镜</t>
+          <t>红点镜</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1580,7 +1580,7 @@
         <v>150</v>
       </c>
       <c r="L21" t="n">
-        <v>530</v>
+        <v>580</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
@@ -1590,6 +1590,11 @@
       </c>
       <c r="O21" t="n">
         <v>2</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Scope/Optic_01</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1598,19 +1603,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>四倍瞄准镜</t>
+          <t>全息镜</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中距离 4 倍变焦,平衡之选。</t>
+          <t>全息瞄准,视野开阔。</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1622,19 +1627,24 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>350</v>
+        <v>180</v>
       </c>
       <c r="L22" t="n">
-        <v>520</v>
+        <v>575</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="O22" t="n">
         <v>2</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Scope/Optic_02</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1643,19 +1653,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>八倍瞄准镜</t>
+          <t>反射镜</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>远距离 8 倍高倍镜,狙击利器。</t>
+          <t>轻便反射镜,出镜迅速。</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1667,19 +1677,24 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="L23" t="n">
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Scope/Optic_03</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1688,12 +1703,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>标准弹药</t>
+          <t>标准弹</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>通用弹药,弹匣容量 12 发。</t>
+          <t>通用弹药,弹匣 12 发。</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1715,7 +1730,7 @@
         <v>80</v>
       </c>
       <c r="L24" t="n">
-        <v>530</v>
+        <v>580</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
@@ -1725,6 +1740,11 @@
       </c>
       <c r="O24" t="n">
         <v>3</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bullet/Bullet_01</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1738,7 +1758,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>高穿透弹药,弹匣容量 20 发。</t>
+          <t>高穿透,弹匣 20 发。</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1760,7 +1780,7 @@
         <v>200</v>
       </c>
       <c r="L25" t="n">
-        <v>520</v>
+        <v>575</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
@@ -1770,6 +1790,11 @@
       </c>
       <c r="O25" t="n">
         <v>3</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bullet/Bullet_02</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1778,19 +1803,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>高爆弹</t>
+          <t>空尖弹</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>高伤害弹药,弹匣容量 30 发。</t>
+          <t>高停止力,弹匣 15 发。</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1799,25 +1824,729 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K26" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="L26" t="n">
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="27"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bullet/Bullet_03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7004</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>二倍镜</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2 倍变焦,近中距通用。</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>300</v>
+      </c>
+      <c r="L27" t="n">
+        <v>565</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>400</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Scope/Optic_04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7005</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>四倍镜</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4 倍变焦,中距精准。</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>380</v>
+      </c>
+      <c r="L28" t="n">
+        <v>560</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>500</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Scope/Optic_05</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7006</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>六倍镜</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6 倍变焦,中远距压制。</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>520</v>
+      </c>
+      <c r="L29" t="n">
+        <v>555</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>700</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Scope/Optic_06</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7007</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>八倍镜</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8 倍高倍镜,远距狙击。</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>700</v>
+      </c>
+      <c r="L30" t="n">
+        <v>550</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>900</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Scope/Optic_07</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7008</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>十倍镜</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10 倍超远倍镜,一击致命。</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>950</v>
+      </c>
+      <c r="L31" t="n">
+        <v>545</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Scope/Optic_08</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>8004</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>散射弹</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>一次多发,弹匣 18 发。</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>18</v>
+      </c>
+      <c r="K32" t="n">
+        <v>180</v>
+      </c>
+      <c r="L32" t="n">
+        <v>565</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>280</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bullet/Bullet_04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>8005</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>高爆弹</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>爆炸伤害,弹匣 30 发。</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>30</v>
+      </c>
+      <c r="K33" t="n">
+        <v>400</v>
+      </c>
+      <c r="L33" t="n">
+        <v>560</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>600</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bullet/Bullet_05</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>8006</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>燃烧弹</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>持续灼烧,弹匣 28 发。</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>28</v>
+      </c>
+      <c r="K34" t="n">
+        <v>360</v>
+      </c>
+      <c r="L34" t="n">
+        <v>555</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>550</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bullet/Bullet_06</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>8007</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>重型弹</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>超大弹匣 35 发。</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>35</v>
+      </c>
+      <c r="K35" t="n">
+        <v>520</v>
+      </c>
+      <c r="L35" t="n">
+        <v>550</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>800</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bullet/Bullet_07</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6005</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>高精狙击枪</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>高精度栓动狙击枪。</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>600</v>
+      </c>
+      <c r="L36" t="n">
+        <v>565</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Weapon/SniperRifle2_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6006</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>远程狙击枪</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>超远射程狙击枪。</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>700</v>
+      </c>
+      <c r="L37" t="n">
+        <v>560</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1400</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Weapon/SniperRifle3_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6007</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>军用狙击枪</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>制式军用狙击枪。</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>800</v>
+      </c>
+      <c r="L38" t="n">
+        <v>555</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1600</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Weapon/SniperRifle4_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6008</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>连发狙击枪</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>半自动连发狙击枪。</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>900</v>
+      </c>
+      <c r="L39" t="n">
+        <v>550</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Weapon/SniperRifle5_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>6009</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>重型狙击枪</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>反器材重型狙击枪。</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L40" t="n">
+        <v>545</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2200</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Weapon/SniperRifle6_01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/excel/3xlsx/item.xlsx
+++ b/tools/excel/3xlsx/item.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -536,6 +536,11 @@
           <t>模型路径</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>惊扰范围</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -618,6 +623,11 @@
           <t>modelPath</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>disturbRange</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -700,6 +710,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -780,6 +795,11 @@
       <c r="P4" t="inlineStr">
         <is>
           <t>client</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -1381,6 +1401,9 @@
           <t>Weapon/AssaultRifle1_01</t>
         </is>
       </c>
+      <c r="Q17" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1436,6 +1459,9 @@
           <t>Weapon/SniperRifle1_01</t>
         </is>
       </c>
+      <c r="Q18" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1491,6 +1517,9 @@
           <t>Weapon/Shotgun1_01</t>
         </is>
       </c>
+      <c r="Q19" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1546,6 +1575,9 @@
           <t>Weapon/Pistol1_01</t>
         </is>
       </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1749,16 +1781,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8002</v>
+        <v>8003</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>穿甲弹</t>
+          <t>空尖弹</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>高穿透,弹匣 20 发。</t>
+          <t>高停止力,弹匣 15 发。</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1774,41 +1806,41 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="L25" t="n">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bullet/Bullet_02</t>
+          <t>Bullet/Bullet_03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>8003</v>
+        <v>7004</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>空尖弹</t>
+          <t>二倍镜</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>高停止力,弹匣 15 发。</t>
+          <t>2 倍变焦,近中距通用。</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1824,41 +1856,41 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="L26" t="n">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bullet/Bullet_03</t>
+          <t>Scope/Optic_04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7004</v>
+        <v>7005</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>二倍镜</t>
+          <t>四倍镜</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2 倍变焦,近中距通用。</t>
+          <t>4 倍变焦,中距精准。</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1877,45 +1909,45 @@
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="L27" t="n">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O27" t="n">
         <v>2</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Scope/Optic_04</t>
+          <t>Scope/Optic_05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7005</v>
+        <v>7006</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>四倍镜</t>
+          <t>六倍镜</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4 倍变焦,中距精准。</t>
+          <t>6 倍变焦,中远距压制。</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -1927,38 +1959,38 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>380</v>
+        <v>520</v>
       </c>
       <c r="L28" t="n">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Scope/Optic_05</t>
+          <t>Scope/Optic_06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7006</v>
+        <v>7007</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六倍镜</t>
+          <t>八倍镜</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6 倍变焦,中远距压制。</t>
+          <t>8 倍高倍镜,远距狙击。</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1977,45 +2009,45 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>520</v>
+        <v>700</v>
       </c>
       <c r="L29" t="n">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="O29" t="n">
         <v>2</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Scope/Optic_06</t>
+          <t>Scope/Optic_07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>7007</v>
+        <v>7008</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>八倍镜</t>
+          <t>十倍镜</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8 倍高倍镜,远距狙击。</t>
+          <t>10 倍超远倍镜,一击致命。</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -2027,48 +2059,48 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>700</v>
+        <v>950</v>
       </c>
       <c r="L30" t="n">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="O30" t="n">
         <v>2</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Scope/Optic_07</t>
+          <t>Scope/Optic_08</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>7008</v>
+        <v>6005</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>十倍镜</t>
+          <t>高精狙击枪</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10 倍超远倍镜,一击致命。</t>
+          <t>高精度栓动狙击枪。</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -2077,10 +2109,10 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>600</v>
       </c>
       <c r="L31" t="n">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -2089,462 +2121,227 @@
         <v>1200</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Scope/Optic_08</t>
-        </is>
+          <t>Weapon/SniperRifle2_01</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>8004</v>
+        <v>6006</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>散射弹</t>
+          <t>远程狙击枪</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>一次多发,弹匣 18 发。</t>
+          <t>超远射程狙击枪。</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="L32" t="n">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>280</v>
+        <v>1400</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bullet/Bullet_04</t>
-        </is>
+          <t>Weapon/SniperRifle3_01</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8005</v>
+        <v>6007</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>高爆弹</t>
+          <t>军用狙击枪</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>爆炸伤害,弹匣 30 发。</t>
+          <t>制式军用狙击枪。</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="L33" t="n">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M33" t="n">
         <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bullet/Bullet_05</t>
-        </is>
+          <t>Weapon/SniperRifle4_01</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8006</v>
+        <v>6008</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>燃烧弹</t>
+          <t>连发狙击枪</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>持续灼烧,弹匣 28 发。</t>
+          <t>半自动连发狙击枪。</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>360</v>
+        <v>900</v>
       </c>
       <c r="L34" t="n">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="M34" t="n">
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>550</v>
+        <v>1800</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bullet/Bullet_06</t>
-        </is>
+          <t>Weapon/SniperRifle5_01</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>8007</v>
+        <v>6009</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>重型弹</t>
+          <t>重型狙击枪</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>超大弹匣 35 发。</t>
+          <t>反器材重型狙击枪。</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>520</v>
+        <v>1200</v>
       </c>
       <c r="L35" t="n">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>800</v>
+        <v>2200</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bullet/Bullet_07</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>6005</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>高精狙击枪</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>高精度栓动狙击枪。</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>600</v>
-      </c>
-      <c r="L36" t="n">
-        <v>565</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1200</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Weapon/SniperRifle2_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>6006</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>远程狙击枪</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>超远射程狙击枪。</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>700</v>
-      </c>
-      <c r="L37" t="n">
-        <v>560</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1400</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Weapon/SniperRifle3_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>6007</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>军用狙击枪</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>制式军用狙击枪。</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>4</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>800</v>
-      </c>
-      <c r="L38" t="n">
-        <v>555</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1600</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Weapon/SniperRifle4_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>6008</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>连发狙击枪</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>半自动连发狙击枪。</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>4</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>900</v>
-      </c>
-      <c r="L39" t="n">
-        <v>550</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1800</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Weapon/SniperRifle5_01</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>6009</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>重型狙击枪</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>反器材重型狙击枪。</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" t="n">
-        <v>5</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L40" t="n">
-        <v>545</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2200</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
           <t>Weapon/SniperRifle6_01</t>
         </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/3xlsx/item.xlsx
+++ b/tools/excel/3xlsx/item.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -541,6 +541,11 @@
           <t>惊扰范围</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>瞄准晃动幅度</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -628,6 +633,11 @@
           <t>disturbRange</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>aimSway</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -715,6 +725,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -798,6 +813,11 @@
         </is>
       </c>
       <c r="Q4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>all</t>
         </is>
@@ -1628,6 +1648,9 @@
           <t>Scope/Optic_01</t>
         </is>
       </c>
+      <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1678,6 +1701,9 @@
           <t>Scope/Optic_02</t>
         </is>
       </c>
+      <c r="R22" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1728,6 +1754,9 @@
           <t>Scope/Optic_03</t>
         </is>
       </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1878,6 +1907,9 @@
           <t>Scope/Optic_04</t>
         </is>
       </c>
+      <c r="R26" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1928,6 +1960,9 @@
           <t>Scope/Optic_05</t>
         </is>
       </c>
+      <c r="R27" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1978,6 +2013,9 @@
           <t>Scope/Optic_06</t>
         </is>
       </c>
+      <c r="R28" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2028,6 +2066,9 @@
           <t>Scope/Optic_07</t>
         </is>
       </c>
+      <c r="R29" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2077,6 +2118,9 @@
         <is>
           <t>Scope/Optic_08</t>
         </is>
+      </c>
+      <c r="R30" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="31">

--- a/tools/excel/3xlsx/item.xlsx
+++ b/tools/excel/3xlsx/item.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -546,6 +546,21 @@
           <t>瞄准晃动幅度</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>弹夹容量</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>备弹</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>连射CD</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -638,6 +653,21 @@
           <t>aimSway</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>magazine</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>reserveAmmo</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>fireCd</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -730,6 +760,21 @@
           <t>float</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -818,6 +863,21 @@
         </is>
       </c>
       <c r="R4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>all</t>
         </is>
@@ -1424,6 +1484,15 @@
       <c r="Q17" t="n">
         <v>14</v>
       </c>
+      <c r="S17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" t="n">
+        <v>120</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1482,6 +1551,15 @@
       <c r="Q18" t="n">
         <v>22</v>
       </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>30</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1540,6 +1618,15 @@
       <c r="Q19" t="n">
         <v>18</v>
       </c>
+      <c r="S19" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>36</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1598,6 +1685,15 @@
       <c r="Q20" t="n">
         <v>7</v>
       </c>
+      <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="n">
+        <v>60</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2175,6 +2271,15 @@
       <c r="Q31" t="n">
         <v>24</v>
       </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>30</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2228,6 +2333,15 @@
       <c r="Q32" t="n">
         <v>26</v>
       </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>25</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2281,6 +2395,15 @@
       <c r="Q33" t="n">
         <v>28</v>
       </c>
+      <c r="S33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" t="n">
+        <v>40</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2334,6 +2457,15 @@
       <c r="Q34" t="n">
         <v>30</v>
       </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>20</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2386,6 +2518,15 @@
       </c>
       <c r="Q35" t="n">
         <v>34</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="n">
+        <v>40</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/3xlsx/item.xlsx
+++ b/tools/excel/3xlsx/item.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1429,23 +1429,23 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>突击步枪</t>
+          <t>狙击枪</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>全自动突击步枪，射速快、弹量足。</t>
+          <t>高倍远程狙击枪，单发高伤。</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1462,65 +1462,60 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="L17" t="n">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Weapon/AssaultRifle1_01</t>
+          <t>Weapon/SniperRifle1_01</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
         <v>30</v>
       </c>
-      <c r="T17" t="n">
-        <v>120</v>
-      </c>
       <c r="U17" t="n">
-        <v>0.12</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6002</v>
+        <v>7002</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>狙击枪</t>
+          <t>全息镜</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>高倍远程狙击枪，单发高伤。</t>
+          <t>全息瞄准,视野开阔。</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>UI/Item/sword_iron</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -1529,74 +1524,60 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="L18" t="n">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Weapon/SniperRifle1_01</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>22</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>30</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.2</v>
+          <t>Scope/Optic_02</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6003</v>
+        <v>8001</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>散弹枪</t>
+          <t>标准弹</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>近距离散射,火力凶猛。</t>
+          <t>通用弹药,弹匣 12 发。</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UI/Item/sword_iron</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="L19" t="n">
         <v>580</v>
@@ -1605,53 +1586,36 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Weapon/Shotgun1_01</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>18</v>
-      </c>
-      <c r="S19" t="n">
-        <v>6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>36</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.8</v>
+          <t>Bullet/Bullet_01</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6004</v>
+        <v>8003</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>手枪</t>
+          <t>空尖弹</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>轻便副武器手枪，出枪迅速。</t>
+          <t>高停止力,弹匣 15 发。</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>UI/Item/sword_iron</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -1660,10 +1624,10 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L20" t="n">
         <v>570</v>
@@ -1672,48 +1636,36 @@
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Weapon/Pistol1_01</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="S20" t="n">
-        <v>12</v>
-      </c>
-      <c r="T20" t="n">
-        <v>60</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.3</v>
+          <t>Bullet/Bullet_03</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7001</v>
+        <v>7005</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>红点镜</t>
+          <t>四倍镜</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>红点全息,快速锁定近距目标。</t>
+          <t>4 倍变焦,中距精准。</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -1725,48 +1677,48 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="L21" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="O21" t="n">
         <v>2</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Scope/Optic_01</t>
+          <t>Scope/Optic_05</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7002</v>
+        <v>7006</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>全息镜</t>
+          <t>六倍镜</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>全息瞄准,视野开阔。</t>
+          <t>6 倍变焦,中远距压制。</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1778,48 +1730,48 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>180</v>
+        <v>520</v>
       </c>
       <c r="L22" t="n">
-        <v>575</v>
+        <v>555</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="O22" t="n">
         <v>2</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Scope/Optic_02</t>
+          <t>Scope/Optic_06</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>1.1</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7003</v>
+        <v>7007</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>反射镜</t>
+          <t>八倍镜</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>轻便反射镜,出镜迅速。</t>
+          <t>8 倍高倍镜,远距狙击。</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1831,48 +1783,48 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="L23" t="n">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="O23" t="n">
         <v>2</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Scope/Optic_03</t>
+          <t>Scope/Optic_07</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8001</v>
+        <v>7008</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>标准弹</t>
+          <t>十倍镜</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>通用弹药,弹匣 12 发。</t>
+          <t>10 倍超远倍镜,一击致命。</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1881,101 +1833,116 @@
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
-        <v>580</v>
+        <v>545</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bullet/Bullet_01</t>
-        </is>
+          <t>Scope/Optic_08</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8003</v>
+        <v>6005</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>空尖弹</t>
+          <t>高精狙击枪</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>高停止力,弹匣 15 发。</t>
+          <t>高精度栓动狙击枪。</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>160</v>
+        <v>600</v>
       </c>
       <c r="L25" t="n">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>250</v>
+        <v>1200</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bullet/Bullet_03</t>
-        </is>
+          <t>Weapon/SniperRifle2_01</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>24</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>30</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7004</v>
+        <v>6006</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>二倍镜</t>
+          <t>远程狙击枪</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2 倍变焦,近中距通用。</t>
+          <t>超远射程狙击枪。</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -1984,51 +1951,60 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="L26" t="n">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Scope/Optic_04</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
-        <v>0.85</v>
+          <t>Weapon/SniperRifle3_01</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>26</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>25</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7005</v>
+        <v>6007</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>四倍镜</t>
+          <t>军用狙击枪</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4 倍变焦,中距精准。</t>
+          <t>制式军用狙击枪。</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -2037,51 +2013,60 @@
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>380</v>
+        <v>800</v>
       </c>
       <c r="L27" t="n">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Scope/Optic_05</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>0.7</v>
+          <t>Weapon/SniperRifle4_01</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>40</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7006</v>
+        <v>6008</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六倍镜</t>
+          <t>连发狙击枪</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6 倍变焦,中远距压制。</t>
+          <t>半自动连发狙击枪。</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -2090,51 +2075,60 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>520</v>
+        <v>900</v>
       </c>
       <c r="L28" t="n">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>700</v>
+        <v>1800</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Scope/Optic_06</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
-        <v>0.55</v>
+          <t>Weapon/SniperRifle5_01</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>30</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>20</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7007</v>
+        <v>6009</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>八倍镜</t>
+          <t>重型狙击枪</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8 倍高倍镜,远距狙击。</t>
+          <t>反器材重型狙击枪。</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -2143,389 +2137,35 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="L29" t="n">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>900</v>
+        <v>2200</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Scope/Optic_07</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>7008</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>十倍镜</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>10 倍超远倍镜,一击致命。</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>950</v>
-      </c>
-      <c r="L30" t="n">
-        <v>545</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1200</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Scope/Optic_08</t>
-        </is>
-      </c>
-      <c r="R30" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>6005</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>高精狙击枪</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>高精度栓动狙击枪。</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>600</v>
-      </c>
-      <c r="L31" t="n">
-        <v>565</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1200</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Weapon/SniperRifle2_01</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>24</v>
-      </c>
-      <c r="S31" t="n">
-        <v>5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>30</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>6006</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>远程狙击枪</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>超远射程狙击枪。</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>700</v>
-      </c>
-      <c r="L32" t="n">
-        <v>560</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1400</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Weapon/SniperRifle3_01</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>26</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>25</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>6007</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>军用狙击枪</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>制式军用狙击枪。</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>4</v>
-      </c>
-      <c r="G33" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>800</v>
-      </c>
-      <c r="L33" t="n">
-        <v>555</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1600</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Weapon/SniperRifle4_01</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>28</v>
-      </c>
-      <c r="S33" t="n">
-        <v>8</v>
-      </c>
-      <c r="T33" t="n">
+          <t>Weapon/SniperRifle6_01</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>34</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="n">
         <v>40</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>6008</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>连发狙击枪</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>半自动连发狙击枪。</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>900</v>
-      </c>
-      <c r="L34" t="n">
-        <v>550</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1800</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Weapon/SniperRifle5_01</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>30</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>20</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>6009</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>重型狙击枪</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>反器材重型狙击枪。</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="n">
-        <v>5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L35" t="n">
-        <v>545</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2200</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Weapon/SniperRifle6_01</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>34</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="n">
-        <v>40</v>
-      </c>
-      <c r="U35" t="n">
+      <c r="U29" t="n">
         <v>0.9</v>
       </c>
     </row>
